--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118293</v>
+        <v>122118299</v>
       </c>
       <c r="B2" t="n">
-        <v>57365</v>
+        <v>90763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543044</v>
+        <v>543105</v>
       </c>
       <c r="R2" t="n">
-        <v>7239359</v>
+        <v>7239400</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +753,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,17 +764,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies # Tunn gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118290</v>
+        <v>122118293</v>
       </c>
       <c r="B3" t="n">
         <v>57365</v>
@@ -835,16 +831,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543065</v>
+        <v>543044</v>
       </c>
       <c r="R3" t="n">
-        <v>7239267</v>
+        <v>7239359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,6 +892,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118292</v>
+        <v>122118296</v>
       </c>
       <c r="B4" t="n">
         <v>57365</v>
@@ -948,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543102</v>
+        <v>543141</v>
       </c>
       <c r="R4" t="n">
-        <v>7239389</v>
+        <v>7239452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118297</v>
+        <v>122118290</v>
       </c>
       <c r="B5" t="n">
         <v>57365</v>
@@ -1055,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543035</v>
+        <v>543065</v>
       </c>
       <c r="R5" t="n">
-        <v>7239362</v>
+        <v>7239267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118296</v>
+        <v>122118289</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
+        <v>90745</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543141</v>
+        <v>543104</v>
       </c>
       <c r="R6" t="n">
-        <v>7239452</v>
+        <v>7239401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,11 +1215,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1213,6 +1223,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1229,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118289</v>
+        <v>122118292</v>
       </c>
       <c r="B7" t="n">
-        <v>90745</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543104</v>
+        <v>543102</v>
       </c>
       <c r="R7" t="n">
-        <v>7239401</v>
+        <v>7239389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,6 +1337,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1315,26 +1350,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1351,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118299</v>
+        <v>122118297</v>
       </c>
       <c r="B8" t="n">
-        <v>90763</v>
+        <v>57365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543105</v>
+        <v>543035</v>
       </c>
       <c r="R8" t="n">
-        <v>7239400</v>
+        <v>7239362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1444,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1437,26 +1457,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunn gran</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118299</v>
+        <v>122118296</v>
       </c>
       <c r="B2" t="n">
-        <v>90763</v>
+        <v>57369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543105</v>
+        <v>543141</v>
       </c>
       <c r="R2" t="n">
-        <v>7239400</v>
+        <v>7239452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunn gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118293</v>
+        <v>122118292</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,20 +816,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543044</v>
+        <v>543102</v>
       </c>
       <c r="R3" t="n">
-        <v>7239359</v>
+        <v>7239389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,21 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -923,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118296</v>
+        <v>122118297</v>
       </c>
       <c r="B4" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543141</v>
+        <v>543035</v>
       </c>
       <c r="R4" t="n">
-        <v>7239452</v>
+        <v>7239362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118290</v>
+        <v>122118289</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543065</v>
+        <v>543104</v>
       </c>
       <c r="R5" t="n">
-        <v>7239267</v>
+        <v>7239401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,11 +1074,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1121,6 +1082,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1137,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118289</v>
+        <v>122118290</v>
       </c>
       <c r="B6" t="n">
-        <v>90745</v>
+        <v>57369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543104</v>
+        <v>543065</v>
       </c>
       <c r="R6" t="n">
-        <v>7239401</v>
+        <v>7239267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,6 +1196,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1223,26 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1259,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118292</v>
+        <v>122118293</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,16 +1259,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543102</v>
+        <v>543044</v>
       </c>
       <c r="R7" t="n">
-        <v>7239389</v>
+        <v>7239359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,6 +1320,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118297</v>
+        <v>122118299</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
+        <v>90772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543035</v>
+        <v>543105</v>
       </c>
       <c r="R8" t="n">
-        <v>7239362</v>
+        <v>7239400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,11 +1429,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1457,6 +1437,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunn gran</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118296</v>
+        <v>122118292</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543141</v>
+        <v>543102</v>
       </c>
       <c r="R2" t="n">
-        <v>7239452</v>
+        <v>7239389</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118297</v>
+        <v>122118296</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543035</v>
+        <v>543141</v>
       </c>
       <c r="R3" t="n">
-        <v>7239362</v>
+        <v>7239452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118289</v>
+        <v>122118290</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543104</v>
+        <v>543065</v>
       </c>
       <c r="R4" t="n">
-        <v>7239401</v>
+        <v>7239267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,6 +967,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,26 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118290</v>
+        <v>122118299</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>90797</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543065</v>
+        <v>543105</v>
       </c>
       <c r="R5" t="n">
-        <v>7239267</v>
+        <v>7239400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,11 +1074,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1102,6 +1082,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunn gran</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118293</v>
+        <v>122118297</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1152,20 +1152,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543044</v>
+        <v>543035</v>
       </c>
       <c r="R6" t="n">
-        <v>7239359</v>
+        <v>7239362</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,21 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1244,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118299</v>
+        <v>122118293</v>
       </c>
       <c r="B7" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,34 +1241,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543105</v>
+        <v>543044</v>
       </c>
       <c r="R7" t="n">
-        <v>7239400</v>
+        <v>7239359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,6 +1307,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1333,22 +1323,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Tunn gran</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1366,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118292</v>
+        <v>122118289</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>90779</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543102</v>
+        <v>543104</v>
       </c>
       <c r="R8" t="n">
-        <v>7239389</v>
+        <v>7239401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,11 +1429,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1457,6 +1437,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118297</v>
+        <v>122118289</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>90779</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543035</v>
+        <v>543104</v>
       </c>
       <c r="R6" t="n">
-        <v>7239362</v>
+        <v>7239401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,11 +1196,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1209,6 +1204,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118293</v>
+        <v>122118297</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1259,20 +1274,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543044</v>
+        <v>543035</v>
       </c>
       <c r="R7" t="n">
-        <v>7239359</v>
+        <v>7239362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,21 +1331,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118289</v>
+        <v>122118293</v>
       </c>
       <c r="B8" t="n">
-        <v>90779</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1363,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543104</v>
+        <v>543044</v>
       </c>
       <c r="R8" t="n">
-        <v>7239401</v>
+        <v>7239359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1429,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1440,22 +1445,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran lutande</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118292</v>
+        <v>122118293</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -709,16 +709,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543102</v>
+        <v>543044</v>
       </c>
       <c r="R2" t="n">
-        <v>7239389</v>
+        <v>7239359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,6 +770,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118296</v>
+        <v>122118290</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -822,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543141</v>
+        <v>543065</v>
       </c>
       <c r="R3" t="n">
-        <v>7239452</v>
+        <v>7239267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118290</v>
+        <v>122118289</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>90789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543065</v>
+        <v>543104</v>
       </c>
       <c r="R4" t="n">
-        <v>7239267</v>
+        <v>7239401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +986,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -980,6 +994,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118299</v>
+        <v>122118297</v>
       </c>
       <c r="B5" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543105</v>
+        <v>543035</v>
       </c>
       <c r="R5" t="n">
-        <v>7239400</v>
+        <v>7239362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1108,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1082,26 +1121,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunn gran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118289</v>
+        <v>122118296</v>
       </c>
       <c r="B6" t="n">
-        <v>90779</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543104</v>
+        <v>543141</v>
       </c>
       <c r="R6" t="n">
-        <v>7239401</v>
+        <v>7239452</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1215,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1204,26 +1228,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1240,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118297</v>
+        <v>122118292</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1280,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543035</v>
+        <v>543102</v>
       </c>
       <c r="R7" t="n">
-        <v>7239362</v>
+        <v>7239389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118293</v>
+        <v>122118299</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,38 +1367,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543044</v>
+        <v>543105</v>
       </c>
       <c r="R8" t="n">
-        <v>7239359</v>
+        <v>7239400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,11 +1429,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1445,17 +1440,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies # Tunn gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118293</v>
+        <v>122118292</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -709,20 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543044</v>
+        <v>543102</v>
       </c>
       <c r="R2" t="n">
-        <v>7239359</v>
+        <v>7239389</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118290</v>
+        <v>122118293</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -835,16 +816,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543065</v>
+        <v>543044</v>
       </c>
       <c r="R3" t="n">
-        <v>7239267</v>
+        <v>7239359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,6 +877,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118289</v>
+        <v>122118290</v>
       </c>
       <c r="B4" t="n">
-        <v>90789</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543104</v>
+        <v>543065</v>
       </c>
       <c r="R4" t="n">
-        <v>7239401</v>
+        <v>7239267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,6 +986,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -994,26 +999,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1030,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118297</v>
+        <v>122118299</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>90807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543035</v>
+        <v>543105</v>
       </c>
       <c r="R5" t="n">
-        <v>7239362</v>
+        <v>7239400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,11 +1093,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1121,6 +1101,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunn gran</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118292</v>
+        <v>122118297</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543102</v>
+        <v>543035</v>
       </c>
       <c r="R7" t="n">
-        <v>7239389</v>
+        <v>7239362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118299</v>
+        <v>122118289</v>
       </c>
       <c r="B8" t="n">
-        <v>90807</v>
+        <v>90789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543105</v>
+        <v>543104</v>
       </c>
       <c r="R8" t="n">
-        <v>7239400</v>
+        <v>7239401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Tunn gran</t>
+          <t>Knäckt gran lutande</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Tunn gran</t>
+          <t>Picea abies # Knäckt gran lutande</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118292</v>
+        <v>122118289</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>90801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543102</v>
+        <v>543104</v>
       </c>
       <c r="R2" t="n">
-        <v>7239389</v>
+        <v>7239401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +753,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118293</v>
+        <v>122118290</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,20 +831,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543044</v>
+        <v>543065</v>
       </c>
       <c r="R3" t="n">
-        <v>7239359</v>
+        <v>7239267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,21 +888,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118290</v>
+        <v>122118297</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543065</v>
+        <v>543035</v>
       </c>
       <c r="R4" t="n">
-        <v>7239267</v>
+        <v>7239362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118299</v>
+        <v>122118292</v>
       </c>
       <c r="B5" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543105</v>
+        <v>543102</v>
       </c>
       <c r="R5" t="n">
-        <v>7239400</v>
+        <v>7239389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,6 +1089,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1101,26 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunn gran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1137,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118296</v>
+        <v>122118293</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,16 +1152,20 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543141</v>
+        <v>543044</v>
       </c>
       <c r="R6" t="n">
-        <v>7239452</v>
+        <v>7239359</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,6 +1213,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118297</v>
+        <v>122118299</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>90819</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543035</v>
+        <v>543105</v>
       </c>
       <c r="R7" t="n">
-        <v>7239362</v>
+        <v>7239400</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,11 +1322,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1335,6 +1330,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunn gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1351,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118289</v>
+        <v>122118296</v>
       </c>
       <c r="B8" t="n">
-        <v>90789</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543104</v>
+        <v>543141</v>
       </c>
       <c r="R8" t="n">
-        <v>7239401</v>
+        <v>7239452</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1444,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1437,26 +1457,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118289</v>
+        <v>122118296</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543104</v>
+        <v>543141</v>
       </c>
       <c r="R2" t="n">
-        <v>7239401</v>
+        <v>7239452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118290</v>
+        <v>122118297</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -837,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543065</v>
+        <v>543035</v>
       </c>
       <c r="R3" t="n">
-        <v>7239267</v>
+        <v>7239362</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118297</v>
+        <v>122118293</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -938,16 +923,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543035</v>
+        <v>543044</v>
       </c>
       <c r="R4" t="n">
-        <v>7239362</v>
+        <v>7239359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,6 +984,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1118,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118293</v>
+        <v>122118299</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>90826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1138,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543044</v>
+        <v>543105</v>
       </c>
       <c r="R6" t="n">
-        <v>7239359</v>
+        <v>7239400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,11 +1200,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1216,17 +1211,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies # Tunn gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118299</v>
+        <v>122118290</v>
       </c>
       <c r="B7" t="n">
-        <v>90819</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543105</v>
+        <v>543065</v>
       </c>
       <c r="R7" t="n">
-        <v>7239400</v>
+        <v>7239267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,6 +1322,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1330,26 +1335,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunn gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118296</v>
+        <v>122118289</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>90808</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543141</v>
+        <v>543104</v>
       </c>
       <c r="R8" t="n">
-        <v>7239452</v>
+        <v>7239401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,11 +1429,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1457,6 +1437,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118296</v>
+        <v>122118297</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543141</v>
+        <v>543035</v>
       </c>
       <c r="R2" t="n">
-        <v>7239452</v>
+        <v>7239362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118297</v>
+        <v>122118296</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543035</v>
+        <v>543141</v>
       </c>
       <c r="R3" t="n">
-        <v>7239362</v>
+        <v>7239452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118297</v>
+        <v>122118292</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543035</v>
+        <v>543102</v>
       </c>
       <c r="R2" t="n">
-        <v>7239362</v>
+        <v>7239389</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -800,11 +795,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118293</v>
+        <v>122118299</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,38 +895,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543044</v>
+        <v>543105</v>
       </c>
       <c r="R4" t="n">
-        <v>7239359</v>
+        <v>7239400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,11 +952,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -985,19 +961,19 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies # Tunn gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1015,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118292</v>
+        <v>122118289</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>90813</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543102</v>
+        <v>543104</v>
       </c>
       <c r="R5" t="n">
-        <v>7239389</v>
+        <v>7239401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,11 +1064,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1106,6 +1072,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran lutande</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1122,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118299</v>
+        <v>122118290</v>
       </c>
       <c r="B6" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543105</v>
+        <v>543065</v>
       </c>
       <c r="R6" t="n">
-        <v>7239400</v>
+        <v>7239267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,6 +1176,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1208,26 +1189,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunn gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1244,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118290</v>
+        <v>122118293</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1262,11 +1223,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1278,16 +1234,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543065</v>
+        <v>543044</v>
       </c>
       <c r="R7" t="n">
-        <v>7239267</v>
+        <v>7239359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,6 +1295,16 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1351,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118289</v>
+        <v>122118297</v>
       </c>
       <c r="B8" t="n">
-        <v>90808</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1337,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543104</v>
+        <v>543035</v>
       </c>
       <c r="R8" t="n">
-        <v>7239401</v>
+        <v>7239362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1394,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1437,26 +1407,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118292</v>
+        <v>122118293</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -704,16 +709,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543102</v>
+        <v>543044</v>
       </c>
       <c r="R2" t="n">
-        <v>7239389</v>
+        <v>7239359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +770,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118296</v>
+        <v>122118292</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,6 +819,11 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -812,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543141</v>
+        <v>543102</v>
       </c>
       <c r="R3" t="n">
-        <v>7239452</v>
+        <v>7239389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118299</v>
+        <v>122118289</v>
       </c>
       <c r="B4" t="n">
-        <v>90831</v>
+        <v>90826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543105</v>
+        <v>543104</v>
       </c>
       <c r="R4" t="n">
-        <v>7239400</v>
+        <v>7239401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,6 +995,11 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -968,12 +1007,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Tunn gran</t>
+          <t>Knäckt gran lutande</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Tunn gran</t>
+          <t>Picea abies # Knäckt gran lutande</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -991,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118289</v>
+        <v>122118297</v>
       </c>
       <c r="B5" t="n">
-        <v>90813</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543104</v>
+        <v>543035</v>
       </c>
       <c r="R5" t="n">
-        <v>7239401</v>
+        <v>7239362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1108,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1072,21 +1121,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1103,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122118290</v>
+        <v>122118296</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,6 +1155,11 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1138,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543065</v>
+        <v>543141</v>
       </c>
       <c r="R6" t="n">
-        <v>7239267</v>
+        <v>7239452</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118293</v>
+        <v>122118290</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,6 +1262,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1234,20 +1278,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543044</v>
+        <v>543065</v>
       </c>
       <c r="R7" t="n">
-        <v>7239359</v>
+        <v>7239267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,16 +1335,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1321,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122118297</v>
+        <v>122118299</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,16 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543035</v>
+        <v>543105</v>
       </c>
       <c r="R8" t="n">
-        <v>7239362</v>
+        <v>7239400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,11 +1429,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1407,6 +1437,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Tunn gran</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunn gran</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56618-2024 artfynd.xlsx
+++ b/artfynd/A 56618-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122118293</v>
+        <v>122118289</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543044</v>
+        <v>543104</v>
       </c>
       <c r="R2" t="n">
-        <v>7239359</v>
+        <v>7239401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +748,6 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,17 +759,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Knäckt gran lutande</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies # Knäckt gran lutande</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122118292</v>
+        <v>122118290</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543102</v>
+        <v>543065</v>
       </c>
       <c r="R3" t="n">
-        <v>7239389</v>
+        <v>7239267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122118289</v>
+        <v>122118292</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543104</v>
+        <v>543102</v>
       </c>
       <c r="R4" t="n">
-        <v>7239401</v>
+        <v>7239389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,6 +967,11 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -994,26 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Knäckt gran lutande</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt gran lutande</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1030,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122118297</v>
+        <v>122118293</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,16 +1025,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsån, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543035</v>
+        <v>543044</v>
       </c>
       <c r="R5" t="n">
-        <v>7239362</v>
+        <v>7239359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,6 +1086,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1140,12 +1120,7 @@
         <v>122118296</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,15 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122118290</v>
+        <v>122118297</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543065</v>
+        <v>543035</v>
       </c>
       <c r="R7" t="n">
-        <v>7239267</v>
+        <v>7239362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,128 +1318,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>122118299</v>
-      </c>
-      <c r="B8" t="n">
-        <v>90844</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Dalsån, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>543105</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7239400</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Tunn gran</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunn gran</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
